--- a/forms/trg/Formulir_TRG_ioprg.xlsx
+++ b/forms/trg/Formulir_TRG_ioprg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B26)</f>
+        <f>COUNTA(Anggota!B5:B27)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F26)</f>
+        <f>COUNTA(Anggota!F5:F27)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,41 +913,37 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Hillman Wirawan, S.Psi., M.M., M.A., Ph.D</t>
+          <t>Prof. Dr. Muhammad Tamar, M.Psi.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>I/O Psychology</t>
+          <t>Department of Psychology, Faculty of Medicine, Universitas Hasanuddin</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Department of Psychology, Faculty of Medicine, Universitas Hasanuddin</t>
+          <t>Social Psychology</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-0160-3108</t>
-        </is>
-      </c>
+      <c r="J5" s="12" t="n"/>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6679236</t>
+          <t>6673126</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57144538500</t>
+          <t>57207821105</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -962,12 +958,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Rezky Ariany Aras, S.Psi., M.Psi., Psikolog</t>
+          <t>Hillman Wirawan, S.Psi., M.M., M.A., Ph.D</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -986,17 +982,17 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-0868-2080</t>
+          <t>0000-0002-0160-3108</t>
         </is>
       </c>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6703914</t>
+          <t>6679236</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>60587831600</t>
+          <t>57144538500</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1011,12 +1007,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dwiana Fajriati Dewi, S.Psi., M.Sc</t>
+          <t>Rezky Ariany Aras, S.Psi., M.Psi., Psikolog</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1033,13 +1029,21 @@
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-0868-2080</t>
+        </is>
+      </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>6819476</t>
-        </is>
-      </c>
-      <c r="L7" s="12" t="n"/>
+          <t>6703914</t>
+        </is>
+      </c>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>60587831600</t>
+        </is>
+      </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1052,12 +1056,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Francesco Cangiano, Ph.D</t>
+          <t>Dwiana Fajriati Dewi, S.Psi., M.Sc</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1067,24 +1071,20 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Rabdan Accademy</t>
+          <t>Department of Psychology, Faculty of Medicine, Universitas Hasanuddin</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>0000-0001-6761-9439</t>
-        </is>
-      </c>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>55682518600</t>
-        </is>
-      </c>
+      <c r="J8" s="12" t="n"/>
+      <c r="K8" s="11" t="inlineStr">
+        <is>
+          <t>6819476</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="n"/>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Francis Gaudreault, Ph.D</t>
+          <t>Francesco Cangiano, Ph.D</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1121,13 +1121,13 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-2540-6667</t>
+          <t>0000-0001-6761-9439</t>
         </is>
       </c>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>57896442500</t>
+          <t>55682518600</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Stephane Michaud, Ph.D</t>
+          <t>Francis Gaudreault, Ph.D</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1157,16 +1157,24 @@
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>London Business School</t>
+          <t>Rabdan Accademy</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="12" t="n"/>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-2540-6667</t>
+        </is>
+      </c>
       <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="n"/>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>57896442500</t>
+        </is>
+      </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1179,12 +1187,12 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Wirdah Khairiyah, S.Psi., M.Si.</t>
+          <t>Stephane Michaud, Ph.D</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1194,7 +1202,7 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Department of Psychology, Faculty of Medicine, Universitas Hasanuddin</t>
+          <t>London Business School</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1216,17 +1224,17 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Novina Sabila Zahra, S.Psi., M.A</t>
+          <t>Wirdah Khairiyah, S.Psi., M.Si.</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Psychometrics</t>
+          <t>I/O Psychology</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -1238,21 +1246,9 @@
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-6122-6180</t>
-        </is>
-      </c>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>6986806</t>
-        </is>
-      </c>
-      <c r="L12" s="11" t="inlineStr">
-        <is>
-          <t>58189516300</t>
-        </is>
-      </c>
+      <c r="J12" s="12" t="n"/>
+      <c r="K12" s="12" t="n"/>
+      <c r="L12" s="12" t="n"/>
       <c r="M12" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1265,31 +1261,43 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Abidzar Gifari</t>
+          <t>Novina Sabila Zahra, S.Psi., M.A</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
+          <t>Psychometrics</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
           <t>Department of Psychology, Faculty of Medicine, Universitas Hasanuddin</t>
         </is>
       </c>
-      <c r="E13" s="11" t="n"/>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>0009-0006-8475-1451</t>
-        </is>
-      </c>
-      <c r="K13" s="12" t="n"/>
-      <c r="L13" s="12" t="n"/>
+          <t>0000-0002-6122-6180</t>
+        </is>
+      </c>
+      <c r="K13" s="11" t="inlineStr">
+        <is>
+          <t>6986806</t>
+        </is>
+      </c>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>58189516300</t>
+        </is>
+      </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1302,12 +1310,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Dentamyra Rayyani Hendra Putri</t>
+          <t>Muhammad Abidzar Gifari</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1322,7 +1330,7 @@
       <c r="I14" s="12" t="n"/>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>0009-0008-4752-4182</t>
+          <t>0009-0006-8475-1451</t>
         </is>
       </c>
       <c r="K14" s="12" t="n"/>
@@ -1337,18 +1345,38 @@
       <c r="A15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Dentamyra Rayyani Hendra Putri</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Department of Psychology, Faculty of Medicine, Universitas Hasanuddin</t>
+        </is>
+      </c>
       <c r="E15" s="11" t="n"/>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n"/>
-      <c r="J15" s="12" t="n"/>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>0009-0008-4752-4182</t>
+        </is>
+      </c>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
-      <c r="M15" s="12" t="n"/>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1537,15 +1565,32 @@
       <c r="L26" s="12" t="n"/>
       <c r="M26" s="12" t="n"/>
     </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
